--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_60_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_60_R6.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. PAJOLA</t>
+          <t>M. MORGAN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3153</v>
+        <v>4.5468</v>
       </c>
       <c r="E2" t="n">
-        <v>1.3569</v>
+        <v>4.1242</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9584</v>
+        <v>0.4225</v>
       </c>
       <c r="G2" t="n">
-        <v>4.9383</v>
+        <v>2.9491</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7864</v>
+        <v>-0.6411</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1519</v>
+        <v>3.5902</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2419</v>
+        <v>3.2996</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0838</v>
+        <v>0.0742</v>
       </c>
       <c r="L2" t="n">
-        <v>2.1581</v>
+        <v>3.2254</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6964</v>
+        <v>-0.3505</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2974</v>
+        <v>-0.7153</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9939</v>
+        <v>0.3648</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q2" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2352</v>
+        <v>0.2034</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4525</v>
+        <v>-0.2475</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7827</v>
+        <v>0.4509</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9304</v>
+        <v>0.9304</v>
       </c>
       <c r="W2" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MORGAN</t>
+          <t>A. PAJOLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.4624</v>
+        <v>4.4147</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0063</v>
+        <v>1.1956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4561</v>
+        <v>3.219</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9491</v>
+        <v>4.9383</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6411</v>
+        <v>1.7864</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5902</v>
+        <v>3.1519</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2996</v>
+        <v>4.2419</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0742</v>
+        <v>2.0838</v>
       </c>
       <c r="L3" t="n">
-        <v>3.2254</v>
+        <v>2.1581</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3505</v>
+        <v>0.6964</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7153</v>
+        <v>-0.2974</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3648</v>
+        <v>0.9939</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4639</v>
+        <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1191</v>
+        <v>1.3346</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3655</v>
+        <v>0.2912</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4846</v>
+        <v>1.0433</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>-0.9304</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. JALLOW</t>
+          <t>A. SMAILAGIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2257</v>
+        <v>3.3421</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4341</v>
+        <v>0.9898</v>
       </c>
       <c r="F4" t="n">
-        <v>3.6599</v>
+        <v>2.3523</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8441</v>
+        <v>-0.9028</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4575</v>
+        <v>-0.3507</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3016</v>
+        <v>-0.5521</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1261</v>
+        <v>-1.4419</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.339</v>
+        <v>-0.0533</v>
       </c>
       <c r="L4" t="n">
-        <v>0.465</v>
+        <v>-1.3887</v>
       </c>
       <c r="M4" t="n">
-        <v>0.718</v>
+        <v>0.5392</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1186</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
         <v>0.8366</v>
       </c>
       <c r="P4" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7374</v>
+        <v>0.6212</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3882</v>
+        <v>0.2873</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3492</v>
+        <v>0.3339</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7886</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5051</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>K. JALLOW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9998</v>
+        <v>2.71</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2772</v>
+        <v>-1.1851</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7226</v>
+        <v>3.8951</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0016</v>
+        <v>0.8441</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4896</v>
+        <v>-0.4575</v>
       </c>
       <c r="I5" t="n">
-        <v>0.512</v>
+        <v>1.3016</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0161</v>
+        <v>0.1261</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8688</v>
+        <v>-0.339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>0.465</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0144</v>
+        <v>0.718</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3792</v>
+        <v>-0.1186</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3648</v>
+        <v>0.8366</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9054</v>
+        <v>1.2217</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4208</v>
+        <v>0.6372</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4846</v>
+        <v>0.5845</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7886</v>
+        <v>-0.2836</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7886</v>
+        <v>0.5051</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. SMAILAGIC</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3923</v>
+        <v>2.4944</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4433</v>
+        <v>0.8053</v>
       </c>
       <c r="F6" t="n">
-        <v>1.949</v>
+        <v>1.689</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9028</v>
+        <v>2.0016</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3507</v>
+        <v>1.4896</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5521</v>
+        <v>0.512</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4419</v>
+        <v>2.0161</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0533</v>
+        <v>1.8688</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3887</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5392</v>
+        <v>-0.0144</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2974</v>
+        <v>-0.3792</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8366</v>
+        <v>0.3648</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5515</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3286</v>
+        <v>0.4</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2592</v>
+        <v>-0.051</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0694</v>
+        <v>0.4509</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0.7886</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3695</v>
+        <v>1.476</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7446</v>
+        <v>2.683</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3751</v>
+        <v>-1.207</v>
       </c>
       <c r="G7" t="n">
         <v>2.664</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8499</v>
+        <v>0.9564</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8363</v>
+        <v>0.7747000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0136</v>
+        <v>0.1817</v>
       </c>
       <c r="V7" t="n">
         <v>-2.1444</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0956</v>
+        <v>0.7086</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6115</v>
+        <v>-1.3009</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7071</v>
+        <v>2.0096</v>
       </c>
       <c r="G8" t="n">
         <v>0.9553</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8597</v>
+        <v>-0.2467</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7389</v>
+        <v>-0.4283</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1208</v>
+        <v>0.1817</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.604</v>
+        <v>-0.1989</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0816</v>
+        <v>-0.9454</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4776</v>
+        <v>0.7465000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0.6988</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9058</v>
+        <v>0.4993</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1202</v>
+        <v>0.016</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2144</v>
+        <v>0.4832</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8608</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. HACKETT</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3281</v>
+        <v>-2.4124</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.433</v>
+        <v>-0.8618</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1049</v>
+        <v>-1.5506</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8073</v>
+        <v>0.1812</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.839</v>
+        <v>-0.0228</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6463</v>
+        <v>0.204</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5611</v>
+        <v>0.3529</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2486</v>
+        <v>0.3564</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8097</v>
+        <v>-0.0035</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2462</v>
+        <v>-0.1717</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5904</v>
+        <v>-0.3792</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8366</v>
+        <v>0.2075</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0876</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0965</v>
+        <v>0.2467</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5149</v>
+        <v>-0.0549</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6114</v>
+        <v>0.3016</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1444</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>D. HACKETT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7491</v>
+        <v>-2.5285</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0977</v>
+        <v>-2.9612</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6514</v>
+        <v>0.4327</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1812</v>
+        <v>0.8073</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0228</v>
+        <v>-0.839</v>
       </c>
       <c r="I11" t="n">
-        <v>0.204</v>
+        <v>1.6463</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3529</v>
+        <v>0.5611</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3564</v>
+        <v>-0.2486</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.0035</v>
+        <v>0.8097</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1717</v>
+        <v>0.2462</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3792</v>
+        <v>-0.5904</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2075</v>
+        <v>0.8366</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.6959</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>1.3917</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0901</v>
+        <v>0.8962</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2908</v>
+        <v>-0.0431</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2008</v>
+        <v>0.9392</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1444</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>14.1794</v>
+        <v>14.5528</v>
       </c>
       <c r="E12" t="n">
-        <v>2.170400000000001</v>
+        <v>2.5435</v>
       </c>
       <c r="F12" t="n">
         <v>12.0091</v>
@@ -1357,7 +1357,7 @@
         <v>15.1369</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7903</v>
+        <v>2.790299999999999</v>
       </c>
       <c r="I12" t="n">
         <v>12.3466</v>
@@ -1369,7 +1369,7 @@
         <v>6.1733</v>
       </c>
       <c r="L12" t="n">
-        <v>6.3397</v>
+        <v>6.339700000000001</v>
       </c>
       <c r="M12" t="n">
         <v>2.6237</v>
@@ -1390,13 +1390,13 @@
         <v>15.077</v>
       </c>
       <c r="S12" t="n">
-        <v>5.7593</v>
+        <v>6.1328</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8083</v>
+        <v>1.1816</v>
       </c>
       <c r="U12" t="n">
-        <v>4.9511</v>
+        <v>4.950899999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.7168</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.4484</v>
+        <v>2.5378</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2802</v>
+        <v>3.0443</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8318</v>
+        <v>-0.5065</v>
       </c>
       <c r="G13" t="n">
         <v>1.4802</v>
@@ -1468,13 +1468,13 @@
         <v>1.6237</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8746</v>
+        <v>-0.7852</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1019</v>
+        <v>-0.3378</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.4474</v>
       </c>
       <c r="V13" t="n">
         <v>2.5387</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8378</v>
+        <v>1.7364</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2797</v>
+        <v>1.9874</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4419</v>
+        <v>-0.251</v>
       </c>
       <c r="G14" t="n">
         <v>-1.9343</v>
@@ -1546,13 +1546,13 @@
         <v>2.3195</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6917</v>
+        <v>-0.7932</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3364</v>
+        <v>-0.6286</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3554</v>
+        <v>-0.1645</v>
       </c>
       <c r="V14" t="n">
         <v>2.1444</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3101</v>
+        <v>-0.1959</v>
       </c>
       <c r="E15" t="n">
-        <v>0.5412</v>
+        <v>-0.1665</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2311</v>
+        <v>-0.0294</v>
       </c>
       <c r="G15" t="n">
         <v>0.059</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1406</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1617</v>
+        <v>-0.5461</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3022</v>
+        <v>-0.1006</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>N. ROGKAVOPOULOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8477</v>
+        <v>-1.0912</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08749999999999999</v>
+        <v>-1.9892</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7602</v>
+        <v>0.8979</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.5184</v>
+        <v>-1.0919</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4715</v>
+        <v>-0.7239</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0469</v>
+        <v>-0.368</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2741</v>
+        <v>-0.9845</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7023</v>
+        <v>-0.1982</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4282</v>
+        <v>-0.7863</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2443</v>
+        <v>-0.1074</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7692</v>
+        <v>-0.5256999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4751</v>
+        <v>0.4183</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5316</v>
+        <v>-0.2133</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9752</v>
+        <v>-0.5228</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4437</v>
+        <v>0.3095</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.7886</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7886</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. ROGKAVOPOULOS</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.9232</v>
+        <v>-1.2538</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9892</v>
+        <v>-0.7841</v>
       </c>
       <c r="F17" t="n">
-        <v>1.066</v>
+        <v>-0.4697</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0919</v>
+        <v>-1.5104</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7239</v>
+        <v>-0.3025</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.368</v>
+        <v>-1.2079</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.9845</v>
+        <v>-0.7527</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1982</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
         <v>-0.7863</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.1074</v>
+        <v>-0.7577</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.3361</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>-0.4216</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0452</v>
+        <v>0.0246</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5228</v>
+        <v>-0.0314</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4775</v>
+        <v>0.056</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0643</v>
+        <v>-1.5025</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3398</v>
+        <v>-0.8116</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7245</v>
+        <v>-0.6909</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7133</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8087</v>
+        <v>0.3705</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7863</v>
+        <v>0.3145</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4054</v>
+        <v>-1.6505</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9021</v>
+        <v>-0.9132</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5033</v>
+        <v>-0.7373</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.5104</v>
+        <v>-1.5184</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3025</v>
+        <v>-1.4715</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2079</v>
+        <v>-0.0469</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7527</v>
+        <v>-0.2741</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0336</v>
+        <v>-0.7023</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7863</v>
+        <v>0.4282</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7577</v>
+        <v>-1.2443</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3361</v>
+        <v>-0.7692</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4216</v>
+        <v>-0.4751</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.127</v>
+        <v>-0.2713</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>0.1496</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0224</v>
+        <v>-0.4208</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.9743</v>
+        <v>-2.018</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7485</v>
+        <v>-1.5126</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2258</v>
+        <v>-0.5054</v>
       </c>
       <c r="G20" t="n">
         <v>-2.4195</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.09089999999999999</v>
+        <v>-0.1346</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7306</v>
+        <v>0.4509</v>
       </c>
       <c r="V20" t="n">
         <v>0.5361</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9729</v>
+        <v>-2.4681</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.3153</v>
+        <v>-3.0794</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3424</v>
+        <v>0.6112</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0161</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1887</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3443</v>
+        <v>-1.1084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1555</v>
+        <v>0.4244</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4591</v>
+        <v>-2.78</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9264</v>
+        <v>-2.5725</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5327</v>
+        <v>-0.2074</v>
       </c>
       <c r="G22" t="n">
         <v>-2.5716</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2639</v>
+        <v>-0.5847</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.0376</v>
+        <v>-0.6838</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2262</v>
+        <v>0.09909999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.1289</v>
+        <v>-4.7071</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2243</v>
+        <v>-3.6345</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9046</v>
+        <v>-1.0726</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9006</v>
@@ -2248,13 +2248,13 @@
         <v>3.0154</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6768</v>
+        <v>-1.2551</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.5604</v>
+        <v>-0.9706</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1164</v>
+        <v>-0.2844</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.1795</v>
+        <v>-13.3929</v>
       </c>
       <c r="E24" t="n">
-        <v>-10.432</v>
+        <v>-10.4319</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.7475</v>
+        <v>-2.9611</v>
       </c>
       <c r="G24" t="n">
         <v>-15.1369</v>
@@ -2326,13 +2326,13 @@
         <v>15.0771</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.7591</v>
+        <v>-4.973000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.9511</v>
+        <v>-4.951000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.8082000000000003</v>
+        <v>-0.02180000000000004</v>
       </c>
       <c r="V24" t="n">
         <v>6.716800000000001</v>
